--- a/Sheet/NPCPiece.xlsx
+++ b/Sheet/NPCPiece.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\Moumi_moz.A.I.c_Documents\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A1122A-275C-49DC-9048-2AD6743EEA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E88718-BDDC-433E-A81F-076B2435EBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="375" windowWidth="21480" windowHeight="13380" xr2:uid="{E85E095F-D53A-49C1-B1AC-8D07E0BF2BF1}"/>
+    <workbookView xWindow="60" yWindow="675" windowWidth="21480" windowHeight="13380" activeTab="1" xr2:uid="{E85E095F-D53A-49C1-B1AC-8D07E0BF2BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,6 +282,35 @@
   </si>
   <si>
     <t>초안 등록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stageRequire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 스테이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 키워드를 NPC에게 부여할 수 있도록 획득하기 위해 클리어해야 하는 스테이지 ID
+* [Stage-ID] 값 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.03.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득 조건 값 추가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,26 +467,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -782,7 +811,7 @@
     <col min="1" max="1" width="2.625" customWidth="1"/>
     <col min="2" max="2" width="5.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
@@ -808,9 +837,15 @@
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="B4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
@@ -866,18 +901,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E303EB0-5D09-4F96-A4ED-77A8140619A6}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="44.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="13.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -885,16 +921,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -902,97 +941,115 @@
         <v>3</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1008,7 +1065,7 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="B2:E10"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
@@ -1019,106 +1076,120 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="11">
+    <row r="8" spans="2:5" ht="40.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="9">
         <v>3</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="9">
+        <v>4</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11">
-        <v>4</v>
-      </c>
-      <c r="C9" s="12" t="s">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="9">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E10" s="11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11">
-        <v>5</v>
-      </c>
-      <c r="C10" s="12" t="s">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="9">
+        <v>6</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E11" s="11" t="s">
         <v>50</v>
       </c>
     </row>
